--- a/formats/xlsx/provinces.xlsx
+++ b/formats/xlsx/provinces.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,41 +413,51 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G78"/>
+  <dimension ref="A1:I78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>name_th</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>name_en</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>prefix_th</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>prefix_en</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
         <is>
           <t>geography_id</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>created_at</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>updated_at</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>deleted_at</t>
         </is>
@@ -479,20 +477,22 @@
           <t>Bangkok</t>
         </is>
       </c>
-      <c r="D2" t="n">
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="n">
         <v>2</v>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>2019-08-09T03:33:09.000+07:00</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>2025-09-20T06:31:26.000+07:00</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>2019-08-09T03:33:09.000+07:00</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>2025-09-20T06:31:26.000+07:00</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -508,20 +508,22 @@
           <t>Samut Prakan</t>
         </is>
       </c>
-      <c r="D3" t="n">
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="n">
         <v>2</v>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>2019-08-09T03:33:09.000+07:00</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>2025-09-20T06:31:26.000+07:00</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>2019-08-09T03:33:09.000+07:00</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>2025-09-20T06:31:26.000+07:00</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -537,20 +539,22 @@
           <t>Nonthaburi</t>
         </is>
       </c>
-      <c r="D4" t="n">
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="n">
         <v>2</v>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>2019-08-09T03:33:09.000+07:00</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>2025-09-20T06:31:26.000+07:00</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>2019-08-09T03:33:09.000+07:00</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>2025-09-20T06:31:26.000+07:00</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -566,20 +570,22 @@
           <t>Pathum Thani</t>
         </is>
       </c>
-      <c r="D5" t="n">
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="n">
         <v>2</v>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>2019-08-09T03:33:09.000+07:00</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>2025-09-20T06:31:26.000+07:00</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>2019-08-09T03:33:09.000+07:00</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>2025-09-20T06:31:26.000+07:00</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -595,20 +601,22 @@
           <t>Phra Nakhon Si Ayutthaya</t>
         </is>
       </c>
-      <c r="D6" t="n">
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="n">
         <v>2</v>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>2019-08-09T03:33:09.000+07:00</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>2025-09-20T06:31:26.000+07:00</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>2019-08-09T03:33:09.000+07:00</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>2025-09-20T06:31:26.000+07:00</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -624,20 +632,22 @@
           <t>Ang Thong</t>
         </is>
       </c>
-      <c r="D7" t="n">
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="n">
         <v>2</v>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>2019-08-09T03:33:09.000+07:00</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>2025-09-20T06:31:26.000+07:00</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2019-08-09T03:33:09.000+07:00</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>2025-09-20T06:31:26.000+07:00</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -653,20 +663,22 @@
           <t>Lopburi</t>
         </is>
       </c>
-      <c r="D8" t="n">
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="n">
         <v>2</v>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>2019-08-09T03:33:09.000+07:00</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>2025-09-20T06:31:26.000+07:00</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2019-08-09T03:33:09.000+07:00</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>2025-09-20T06:31:26.000+07:00</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -682,20 +694,22 @@
           <t>Sing Buri</t>
         </is>
       </c>
-      <c r="D9" t="n">
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="n">
         <v>2</v>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>2019-08-09T03:33:09.000+07:00</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>2025-09-20T06:31:26.000+07:00</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>2019-08-09T03:33:09.000+07:00</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>2025-09-20T06:31:26.000+07:00</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -711,20 +725,22 @@
           <t>Chai Nat</t>
         </is>
       </c>
-      <c r="D10" t="n">
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="n">
         <v>2</v>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>2019-08-09T03:33:09.000+07:00</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>2025-09-20T06:31:26.000+07:00</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>2019-08-09T03:33:09.000+07:00</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>2025-09-20T06:31:26.000+07:00</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -740,20 +756,22 @@
           <t>Saraburi</t>
         </is>
       </c>
-      <c r="D11" t="n">
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="n">
         <v>2</v>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>2019-08-09T03:33:09.000+07:00</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>2025-09-20T06:31:26.000+07:00</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>2019-08-09T03:33:09.000+07:00</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>2025-09-20T06:31:26.000+07:00</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -769,20 +787,22 @@
           <t>Chon Buri</t>
         </is>
       </c>
-      <c r="D12" t="n">
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="n">
         <v>5</v>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>2019-08-09T03:33:09.000+07:00</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>2025-09-20T06:31:26.000+07:00</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>2019-08-09T03:33:09.000+07:00</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>2025-09-20T06:31:26.000+07:00</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -798,20 +818,22 @@
           <t>Rayong</t>
         </is>
       </c>
-      <c r="D13" t="n">
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="n">
         <v>5</v>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>2019-08-09T03:33:09.000+07:00</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>2025-09-20T06:31:26.000+07:00</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>2019-08-09T03:33:09.000+07:00</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>2025-09-20T06:31:26.000+07:00</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -827,20 +849,22 @@
           <t>Chanthaburi</t>
         </is>
       </c>
-      <c r="D14" t="n">
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="n">
         <v>5</v>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>2019-08-09T03:33:09.000+07:00</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>2025-09-20T06:31:26.000+07:00</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>2019-08-09T03:33:09.000+07:00</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>2025-09-20T06:31:26.000+07:00</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -856,20 +880,22 @@
           <t>Trat</t>
         </is>
       </c>
-      <c r="D15" t="n">
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="n">
         <v>5</v>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>2019-08-09T03:33:09.000+07:00</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>2025-09-20T06:31:26.000+07:00</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>2019-08-09T03:33:09.000+07:00</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>2025-09-20T06:31:26.000+07:00</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -885,20 +911,22 @@
           <t>Chachoengsao</t>
         </is>
       </c>
-      <c r="D16" t="n">
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="n">
         <v>5</v>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>2019-08-09T03:33:09.000+07:00</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>2025-09-20T06:31:26.000+07:00</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>2019-08-09T03:33:09.000+07:00</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>2025-09-20T06:31:26.000+07:00</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -914,20 +942,22 @@
           <t>Prachin Buri</t>
         </is>
       </c>
-      <c r="D17" t="n">
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="n">
         <v>5</v>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>2019-08-09T03:33:09.000+07:00</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>2025-09-20T06:31:26.000+07:00</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>2019-08-09T03:33:09.000+07:00</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>2025-09-20T06:31:26.000+07:00</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -943,20 +973,22 @@
           <t>Nakhon Nayok</t>
         </is>
       </c>
-      <c r="D18" t="n">
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="n">
         <v>2</v>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>2019-08-09T03:33:09.000+07:00</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>2025-09-20T06:31:26.000+07:00</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>2019-08-09T03:33:09.000+07:00</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>2025-09-20T06:31:26.000+07:00</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -972,20 +1004,22 @@
           <t>Sa Kaeo</t>
         </is>
       </c>
-      <c r="D19" t="n">
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="n">
         <v>5</v>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>2019-08-09T03:33:09.000+07:00</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>2025-09-20T06:31:26.000+07:00</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>2019-08-09T03:33:09.000+07:00</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>2025-09-20T06:31:26.000+07:00</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1001,20 +1035,22 @@
           <t>Nakhon Ratchasima</t>
         </is>
       </c>
-      <c r="D20" t="n">
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="n">
         <v>3</v>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>2019-08-09T03:33:09.000+07:00</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>2025-09-20T06:31:26.000+07:00</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>2019-08-09T03:33:09.000+07:00</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>2025-09-20T06:31:26.000+07:00</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1030,20 +1066,22 @@
           <t>Buri Ram</t>
         </is>
       </c>
-      <c r="D21" t="n">
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="n">
         <v>3</v>
       </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>2019-08-09T03:33:09.000+07:00</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>2025-09-20T06:31:26.000+07:00</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>2019-08-09T03:33:09.000+07:00</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>2025-09-20T06:31:26.000+07:00</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1059,20 +1097,22 @@
           <t>Surin</t>
         </is>
       </c>
-      <c r="D22" t="n">
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="n">
         <v>3</v>
       </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>2019-08-09T03:33:09.000+07:00</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>2025-09-20T06:31:26.000+07:00</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>2019-08-09T03:33:09.000+07:00</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>2025-09-20T06:31:26.000+07:00</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1088,20 +1128,22 @@
           <t>Si Sa Ket</t>
         </is>
       </c>
-      <c r="D23" t="n">
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="n">
         <v>3</v>
       </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>2019-08-09T03:33:09.000+07:00</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>2025-09-20T06:31:26.000+07:00</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>2019-08-09T03:33:09.000+07:00</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>2025-09-20T06:31:26.000+07:00</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1117,20 +1159,22 @@
           <t>Ubon Ratchathani</t>
         </is>
       </c>
-      <c r="D24" t="n">
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="n">
         <v>3</v>
       </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>2019-08-09T03:33:09.000+07:00</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>2025-09-20T06:31:26.000+07:00</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>2019-08-09T03:33:09.000+07:00</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>2025-09-20T06:31:26.000+07:00</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1146,20 +1190,22 @@
           <t>Yasothon</t>
         </is>
       </c>
-      <c r="D25" t="n">
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="n">
         <v>3</v>
       </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>2019-08-09T03:33:09.000+07:00</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>2025-09-20T06:31:26.000+07:00</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>2019-08-09T03:33:09.000+07:00</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>2025-09-20T06:31:26.000+07:00</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1175,20 +1221,22 @@
           <t>Chaiyaphum</t>
         </is>
       </c>
-      <c r="D26" t="n">
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="n">
         <v>3</v>
       </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>2019-08-09T03:33:09.000+07:00</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>2025-09-20T06:31:26.000+07:00</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>2019-08-09T03:33:09.000+07:00</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>2025-09-20T06:31:26.000+07:00</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1204,20 +1252,22 @@
           <t>Amnat Charoen</t>
         </is>
       </c>
-      <c r="D27" t="n">
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="n">
         <v>3</v>
       </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>2019-08-09T03:33:09.000+07:00</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>2025-09-20T06:31:26.000+07:00</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>2019-08-09T03:33:09.000+07:00</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>2025-09-20T06:31:26.000+07:00</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1233,20 +1283,22 @@
           <t>Nong Bua Lam Phu</t>
         </is>
       </c>
-      <c r="D28" t="n">
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="n">
         <v>3</v>
       </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>2019-08-09T03:33:09.000+07:00</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>2025-09-20T06:31:26.000+07:00</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>2019-08-09T03:33:09.000+07:00</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>2025-09-20T06:31:26.000+07:00</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1262,20 +1314,22 @@
           <t>Khon Kaen</t>
         </is>
       </c>
-      <c r="D29" t="n">
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="n">
         <v>3</v>
       </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>2019-08-09T03:33:09.000+07:00</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>2025-09-20T06:31:26.000+07:00</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>2019-08-09T03:33:09.000+07:00</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>2025-09-20T06:31:26.000+07:00</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -1291,20 +1345,22 @@
           <t>Udon Thani</t>
         </is>
       </c>
-      <c r="D30" t="n">
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="n">
         <v>3</v>
       </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>2019-08-09T03:33:09.000+07:00</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>2025-09-20T06:31:26.000+07:00</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>2019-08-09T03:33:09.000+07:00</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>2025-09-20T06:31:26.000+07:00</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1320,20 +1376,22 @@
           <t>Loei</t>
         </is>
       </c>
-      <c r="D31" t="n">
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="n">
         <v>3</v>
       </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>2019-08-09T03:33:09.000+07:00</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>2025-09-20T06:31:26.000+07:00</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>2019-08-09T03:33:09.000+07:00</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>2025-09-20T06:31:26.000+07:00</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -1349,20 +1407,22 @@
           <t>Nong Khai</t>
         </is>
       </c>
-      <c r="D32" t="n">
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="n">
         <v>3</v>
       </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>2019-08-09T03:33:09.000+07:00</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>2025-09-20T06:31:26.000+07:00</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>2019-08-09T03:33:09.000+07:00</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>2025-09-20T06:31:26.000+07:00</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -1378,20 +1438,22 @@
           <t>Maha Sarakham</t>
         </is>
       </c>
-      <c r="D33" t="n">
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="n">
         <v>3</v>
       </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>2019-08-09T03:33:09.000+07:00</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>2025-09-20T06:31:26.000+07:00</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>2019-08-09T03:33:09.000+07:00</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>2025-09-20T06:31:26.000+07:00</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -1407,20 +1469,22 @@
           <t>Roi Et</t>
         </is>
       </c>
-      <c r="D34" t="n">
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="n">
         <v>3</v>
       </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>2019-08-09T03:33:09.000+07:00</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>2025-09-20T06:31:26.000+07:00</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>2019-08-09T03:33:09.000+07:00</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>2025-09-20T06:31:26.000+07:00</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -1436,20 +1500,22 @@
           <t>Kalasin</t>
         </is>
       </c>
-      <c r="D35" t="n">
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="n">
         <v>3</v>
       </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>2019-08-09T03:33:09.000+07:00</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>2025-09-20T06:31:26.000+07:00</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>2019-08-09T03:33:09.000+07:00</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>2025-09-20T06:31:26.000+07:00</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -1465,20 +1531,22 @@
           <t>Sakon Nakhon</t>
         </is>
       </c>
-      <c r="D36" t="n">
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="n">
         <v>3</v>
       </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>2019-08-09T03:33:09.000+07:00</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>2025-09-20T06:31:26.000+07:00</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>2019-08-09T03:33:09.000+07:00</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>2025-09-20T06:31:26.000+07:00</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -1494,20 +1562,22 @@
           <t>Nakhon Phanom</t>
         </is>
       </c>
-      <c r="D37" t="n">
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="n">
         <v>3</v>
       </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>2019-08-09T03:33:09.000+07:00</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>2025-09-20T06:31:26.000+07:00</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>2019-08-09T03:33:09.000+07:00</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>2025-09-20T06:31:26.000+07:00</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -1523,20 +1593,22 @@
           <t>Mukdahan</t>
         </is>
       </c>
-      <c r="D38" t="n">
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="n">
         <v>3</v>
       </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>2019-08-09T03:33:09.000+07:00</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>2025-09-20T06:31:26.000+07:00</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>2019-08-09T03:33:09.000+07:00</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>2025-09-20T06:31:26.000+07:00</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -1552,20 +1624,22 @@
           <t>Chiang Mai</t>
         </is>
       </c>
-      <c r="D39" t="n">
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="n">
         <v>1</v>
       </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>2019-08-09T03:33:09.000+07:00</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>2025-09-20T06:31:26.000+07:00</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>2019-08-09T03:33:09.000+07:00</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>2025-09-20T06:31:26.000+07:00</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -1581,20 +1655,22 @@
           <t>Lamphun</t>
         </is>
       </c>
-      <c r="D40" t="n">
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="n">
         <v>1</v>
       </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>2019-08-09T03:33:09.000+07:00</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>2025-09-20T06:31:26.000+07:00</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>2019-08-09T03:33:09.000+07:00</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>2025-09-20T06:31:26.000+07:00</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -1610,20 +1686,22 @@
           <t>Lampang</t>
         </is>
       </c>
-      <c r="D41" t="n">
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="n">
         <v>1</v>
       </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>2019-08-09T03:33:09.000+07:00</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>2025-09-20T06:31:26.000+07:00</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>2019-08-09T03:33:09.000+07:00</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>2025-09-20T06:31:26.000+07:00</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -1639,20 +1717,22 @@
           <t>Uttaradit</t>
         </is>
       </c>
-      <c r="D42" t="n">
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="n">
         <v>1</v>
       </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>2019-08-09T03:33:09.000+07:00</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>2025-09-20T06:31:26.000+07:00</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>2019-08-09T03:33:09.000+07:00</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>2025-09-20T06:31:26.000+07:00</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -1668,20 +1748,22 @@
           <t>Phrae</t>
         </is>
       </c>
-      <c r="D43" t="n">
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="n">
         <v>1</v>
       </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>2019-08-09T03:33:09.000+07:00</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>2025-09-20T06:31:26.000+07:00</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>2019-08-09T03:33:09.000+07:00</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>2025-09-20T06:31:26.000+07:00</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -1697,20 +1779,22 @@
           <t>Nan</t>
         </is>
       </c>
-      <c r="D44" t="n">
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="n">
         <v>1</v>
       </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>2019-08-09T03:33:09.000+07:00</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>2025-09-20T06:31:26.000+07:00</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr"/>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>2019-08-09T03:33:09.000+07:00</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>2025-09-20T06:31:26.000+07:00</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -1726,20 +1810,22 @@
           <t>Phayao</t>
         </is>
       </c>
-      <c r="D45" t="n">
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="n">
         <v>1</v>
       </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>2019-08-09T03:33:09.000+07:00</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>2025-09-20T06:31:26.000+07:00</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr"/>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>2019-08-09T03:33:09.000+07:00</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>2025-09-20T06:31:26.000+07:00</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -1755,20 +1841,22 @@
           <t>Chiang Rai</t>
         </is>
       </c>
-      <c r="D46" t="n">
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="n">
         <v>1</v>
       </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>2019-08-09T03:33:09.000+07:00</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>2025-09-20T06:31:26.000+07:00</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr"/>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>2019-08-09T03:33:09.000+07:00</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>2025-09-20T06:31:26.000+07:00</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -1784,20 +1872,22 @@
           <t>Mae Hong Son</t>
         </is>
       </c>
-      <c r="D47" t="n">
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" t="n">
         <v>1</v>
       </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>2019-08-09T03:33:09.000+07:00</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>2025-09-20T06:31:26.000+07:00</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr"/>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>2019-08-09T03:33:09.000+07:00</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>2025-09-20T06:31:26.000+07:00</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -1813,20 +1903,22 @@
           <t>Nakhon Sawan</t>
         </is>
       </c>
-      <c r="D48" t="n">
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr"/>
+      <c r="F48" t="n">
         <v>2</v>
       </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>2019-08-09T03:33:09.000+07:00</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>2025-09-20T06:31:26.000+07:00</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr"/>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>2019-08-09T03:33:09.000+07:00</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>2025-09-20T06:31:26.000+07:00</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -1842,20 +1934,22 @@
           <t>Uthai Thani</t>
         </is>
       </c>
-      <c r="D49" t="n">
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr"/>
+      <c r="F49" t="n">
         <v>2</v>
       </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>2019-08-09T03:33:09.000+07:00</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>2025-09-20T06:31:26.000+07:00</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr"/>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>2019-08-09T03:33:09.000+07:00</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>2025-09-20T06:31:26.000+07:00</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -1871,20 +1965,22 @@
           <t>Kamphaeng Phet</t>
         </is>
       </c>
-      <c r="D50" t="n">
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr"/>
+      <c r="F50" t="n">
         <v>2</v>
       </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>2019-08-09T03:33:09.000+07:00</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>2025-09-20T06:31:26.000+07:00</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr"/>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>2019-08-09T03:33:09.000+07:00</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>2025-09-20T06:31:26.000+07:00</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -1900,20 +1996,22 @@
           <t>Tak</t>
         </is>
       </c>
-      <c r="D51" t="n">
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" t="n">
         <v>4</v>
       </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>2019-08-09T03:33:09.000+07:00</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>2025-09-20T06:31:26.000+07:00</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr"/>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>2019-08-09T03:33:09.000+07:00</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>2025-09-20T06:31:26.000+07:00</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -1929,20 +2027,22 @@
           <t>Sukhothai</t>
         </is>
       </c>
-      <c r="D52" t="n">
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr"/>
+      <c r="F52" t="n">
         <v>2</v>
       </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>2019-08-09T03:33:09.000+07:00</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>2025-09-20T06:31:26.000+07:00</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr"/>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>2019-08-09T03:33:09.000+07:00</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>2025-09-20T06:31:26.000+07:00</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -1958,20 +2058,22 @@
           <t>Phitsanulok</t>
         </is>
       </c>
-      <c r="D53" t="n">
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr"/>
+      <c r="F53" t="n">
         <v>2</v>
       </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>2019-08-09T03:33:09.000+07:00</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>2025-09-20T06:31:26.000+07:00</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>2019-08-09T03:33:09.000+07:00</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>2025-09-20T06:31:26.000+07:00</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -1987,20 +2089,22 @@
           <t>Phichit</t>
         </is>
       </c>
-      <c r="D54" t="n">
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr"/>
+      <c r="F54" t="n">
         <v>2</v>
       </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>2019-08-09T03:33:09.000+07:00</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>2025-09-20T06:31:26.000+07:00</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr"/>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>2019-08-09T03:33:09.000+07:00</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>2025-09-20T06:31:26.000+07:00</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -2016,20 +2120,22 @@
           <t>Phetchabun</t>
         </is>
       </c>
-      <c r="D55" t="n">
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" t="n">
         <v>2</v>
       </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>2019-08-09T03:33:09.000+07:00</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>2025-09-20T06:31:26.000+07:00</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr"/>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>2019-08-09T03:33:09.000+07:00</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>2025-09-20T06:31:26.000+07:00</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -2045,20 +2151,22 @@
           <t>Ratchaburi</t>
         </is>
       </c>
-      <c r="D56" t="n">
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr"/>
+      <c r="F56" t="n">
         <v>4</v>
       </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>2019-08-09T03:33:09.000+07:00</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>2025-09-20T06:31:26.000+07:00</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr"/>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>2019-08-09T03:33:09.000+07:00</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>2025-09-20T06:31:26.000+07:00</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -2074,20 +2182,22 @@
           <t>Kanchanaburi</t>
         </is>
       </c>
-      <c r="D57" t="n">
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr"/>
+      <c r="F57" t="n">
         <v>4</v>
       </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>2019-08-09T03:33:09.000+07:00</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>2025-09-20T06:31:26.000+07:00</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr"/>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>2019-08-09T03:33:09.000+07:00</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>2025-09-20T06:31:26.000+07:00</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -2103,20 +2213,22 @@
           <t>Suphan Buri</t>
         </is>
       </c>
-      <c r="D58" t="n">
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr"/>
+      <c r="F58" t="n">
         <v>2</v>
       </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>2019-08-09T03:33:09.000+07:00</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>2025-09-20T06:31:26.000+07:00</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>2019-08-09T03:33:09.000+07:00</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>2025-09-20T06:31:26.000+07:00</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -2132,20 +2244,22 @@
           <t>Nakhon Pathom</t>
         </is>
       </c>
-      <c r="D59" t="n">
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr"/>
+      <c r="F59" t="n">
         <v>2</v>
       </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>2019-08-09T03:33:09.000+07:00</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>2025-09-20T06:31:26.000+07:00</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr"/>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>2019-08-09T03:33:09.000+07:00</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>2025-09-20T06:31:26.000+07:00</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -2161,20 +2275,22 @@
           <t>Samut Sakhon</t>
         </is>
       </c>
-      <c r="D60" t="n">
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr"/>
+      <c r="F60" t="n">
         <v>2</v>
       </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>2019-08-09T03:33:09.000+07:00</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>2025-09-20T06:31:26.000+07:00</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr"/>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>2019-08-09T03:33:09.000+07:00</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>2025-09-20T06:31:26.000+07:00</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -2190,20 +2306,22 @@
           <t>Samut Songkhram</t>
         </is>
       </c>
-      <c r="D61" t="n">
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr"/>
+      <c r="F61" t="n">
         <v>2</v>
       </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>2019-08-09T03:33:09.000+07:00</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>2025-09-20T06:31:26.000+07:00</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr"/>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>2019-08-09T03:33:09.000+07:00</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>2025-09-20T06:31:26.000+07:00</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -2219,20 +2337,22 @@
           <t>Phetchaburi</t>
         </is>
       </c>
-      <c r="D62" t="n">
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" t="n">
         <v>4</v>
       </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>2019-08-09T03:33:09.000+07:00</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>2025-09-20T06:31:26.000+07:00</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr"/>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>2019-08-09T03:33:09.000+07:00</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>2025-09-20T06:31:26.000+07:00</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -2248,20 +2368,22 @@
           <t>Prachuap Khiri Khan</t>
         </is>
       </c>
-      <c r="D63" t="n">
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr"/>
+      <c r="F63" t="n">
         <v>4</v>
       </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>2019-08-09T03:33:09.000+07:00</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>2025-09-20T06:31:26.000+07:00</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr"/>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>2019-08-09T03:33:09.000+07:00</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>2025-09-20T06:31:26.000+07:00</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -2277,20 +2399,22 @@
           <t>Nakhon Si Thammarat</t>
         </is>
       </c>
-      <c r="D64" t="n">
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr"/>
+      <c r="F64" t="n">
         <v>6</v>
       </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>2019-08-09T03:33:09.000+07:00</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>2025-09-20T06:31:26.000+07:00</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr"/>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>2019-08-09T03:33:09.000+07:00</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>2025-09-20T06:31:26.000+07:00</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -2306,20 +2430,22 @@
           <t>Krabi</t>
         </is>
       </c>
-      <c r="D65" t="n">
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="inlineStr"/>
+      <c r="F65" t="n">
         <v>6</v>
       </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>2019-08-09T03:33:09.000+07:00</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>2025-09-20T06:31:26.000+07:00</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr"/>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>2019-08-09T03:33:09.000+07:00</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>2025-09-20T06:31:26.000+07:00</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -2335,20 +2461,22 @@
           <t>Phangnga</t>
         </is>
       </c>
-      <c r="D66" t="n">
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr"/>
+      <c r="F66" t="n">
         <v>6</v>
       </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>2019-08-09T03:33:09.000+07:00</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>2025-09-20T06:31:26.000+07:00</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr"/>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>2019-08-09T03:33:09.000+07:00</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>2025-09-20T06:31:26.000+07:00</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -2364,20 +2492,22 @@
           <t>Phuket</t>
         </is>
       </c>
-      <c r="D67" t="n">
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr"/>
+      <c r="F67" t="n">
         <v>6</v>
       </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>2019-08-09T03:33:09.000+07:00</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>2025-09-20T06:31:26.000+07:00</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr"/>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>2019-08-09T03:33:09.000+07:00</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>2025-09-20T06:31:26.000+07:00</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -2393,20 +2523,22 @@
           <t>Surat Thani</t>
         </is>
       </c>
-      <c r="D68" t="n">
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="inlineStr"/>
+      <c r="F68" t="n">
         <v>6</v>
       </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>2019-08-09T03:33:09.000+07:00</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>2025-09-20T06:31:26.000+07:00</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr"/>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>2019-08-09T03:33:09.000+07:00</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>2025-09-20T06:31:26.000+07:00</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -2422,20 +2554,22 @@
           <t>Ranong</t>
         </is>
       </c>
-      <c r="D69" t="n">
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="inlineStr"/>
+      <c r="F69" t="n">
         <v>6</v>
       </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>2019-08-09T03:33:09.000+07:00</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>2025-09-20T06:31:26.000+07:00</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr"/>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>2019-08-09T03:33:09.000+07:00</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>2025-09-20T06:31:26.000+07:00</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -2451,20 +2585,22 @@
           <t>Chumphon</t>
         </is>
       </c>
-      <c r="D70" t="n">
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="inlineStr"/>
+      <c r="F70" t="n">
         <v>6</v>
       </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>2019-08-09T03:33:09.000+07:00</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>2025-09-20T06:31:26.000+07:00</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr"/>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>2019-08-09T03:33:09.000+07:00</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>2025-09-20T06:31:26.000+07:00</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -2480,20 +2616,22 @@
           <t>Songkhla</t>
         </is>
       </c>
-      <c r="D71" t="n">
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="inlineStr"/>
+      <c r="F71" t="n">
         <v>6</v>
       </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>2019-08-09T03:33:09.000+07:00</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>2025-09-20T06:31:26.000+07:00</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr"/>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>2019-08-09T03:33:09.000+07:00</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>2025-09-20T06:31:26.000+07:00</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -2509,20 +2647,22 @@
           <t>Satun</t>
         </is>
       </c>
-      <c r="D72" t="n">
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" t="inlineStr"/>
+      <c r="F72" t="n">
         <v>6</v>
       </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>2019-08-09T03:33:09.000+07:00</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>2025-09-20T06:31:26.000+07:00</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr"/>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>2019-08-09T03:33:09.000+07:00</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>2025-09-20T06:31:26.000+07:00</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -2538,20 +2678,22 @@
           <t>Trang</t>
         </is>
       </c>
-      <c r="D73" t="n">
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="inlineStr"/>
+      <c r="F73" t="n">
         <v>6</v>
       </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>2019-08-09T03:33:09.000+07:00</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>2025-09-20T06:31:26.000+07:00</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr"/>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>2019-08-09T03:33:09.000+07:00</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>2025-09-20T06:31:26.000+07:00</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -2567,20 +2709,22 @@
           <t>Phatthalung</t>
         </is>
       </c>
-      <c r="D74" t="n">
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="inlineStr"/>
+      <c r="F74" t="n">
         <v>6</v>
       </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>2019-08-09T03:33:09.000+07:00</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>2025-09-20T06:31:26.000+07:00</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr"/>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>2019-08-09T03:33:09.000+07:00</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>2025-09-20T06:31:26.000+07:00</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -2596,20 +2740,22 @@
           <t>Pattani</t>
         </is>
       </c>
-      <c r="D75" t="n">
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" t="inlineStr"/>
+      <c r="F75" t="n">
         <v>6</v>
       </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>2019-08-09T03:33:09.000+07:00</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>2025-09-20T06:31:26.000+07:00</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr"/>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>2019-08-09T03:33:09.000+07:00</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>2025-09-20T06:31:26.000+07:00</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -2625,20 +2771,22 @@
           <t>Yala</t>
         </is>
       </c>
-      <c r="D76" t="n">
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="inlineStr"/>
+      <c r="F76" t="n">
         <v>6</v>
       </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>2019-08-09T03:33:09.000+07:00</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>2025-09-20T06:31:26.000+07:00</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr"/>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>2019-08-09T03:33:09.000+07:00</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>2025-09-20T06:31:26.000+07:00</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -2654,20 +2802,22 @@
           <t>Narathiwat</t>
         </is>
       </c>
-      <c r="D77" t="n">
+      <c r="D77" t="inlineStr"/>
+      <c r="E77" t="inlineStr"/>
+      <c r="F77" t="n">
         <v>6</v>
       </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>2019-08-09T03:33:09.000+07:00</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>2025-09-20T06:31:26.000+07:00</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr"/>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>2019-08-09T03:33:09.000+07:00</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>2025-09-20T06:31:26.000+07:00</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -2683,20 +2833,22 @@
           <t>Bueng Kan</t>
         </is>
       </c>
-      <c r="D78" t="n">
+      <c r="D78" t="inlineStr"/>
+      <c r="E78" t="inlineStr"/>
+      <c r="F78" t="n">
         <v>3</v>
       </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>2019-08-09T03:33:09.000+07:00</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>2025-09-20T06:31:26.000+07:00</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr"/>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>2019-08-09T03:33:09.000+07:00</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>2025-09-20T06:31:26.000+07:00</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
